--- a/data/trans_camb/IP21-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,27</t>
+          <t>-2,82; 3,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 3,52</t>
+          <t>-2,84; 3,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,18</t>
+          <t>-3,95; 1,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,93</t>
+          <t>-3,16; 5,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,1</t>
+          <t>-2,6; 5,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1,89</t>
+          <t>-4,7; 1,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,02</t>
+          <t>-2,18; 3,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,38</t>
+          <t>-1,92; 3,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,78</t>
+          <t>-3,31; 0,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,98; 277,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,53; 270,84</t>
+          <t>-74,99; 253,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,17; 165,76</t>
+          <t>-85,67; 234,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,25; 272,93</t>
+          <t>-63,63; 312,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 279,64</t>
+          <t>-56,12; 318,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,1; 142,85</t>
+          <t>-86,93; 133,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 156,04</t>
+          <t>-51,43; 161,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 176,96</t>
+          <t>-45,96; 163,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 42,25</t>
+          <t>-76,16; 63,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 2,66</t>
+          <t>-4,16; 2,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,73</t>
+          <t>-4,77; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -2,18</t>
+          <t>-7,98; -2,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,19</t>
+          <t>-4,59; 1,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,98</t>
+          <t>-5,19; 0,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,18</t>
+          <t>-5,67; 0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,0</t>
+          <t>-3,58; 1,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,39</t>
+          <t>-3,98; 0,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -1,74</t>
+          <t>-5,68; -1,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 64,74</t>
+          <t>-54,54; 71,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 51,84</t>
+          <t>-61,39; 58,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-94,99; -35,55</t>
+          <t>-100,0; -38,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,11; 41,89</t>
+          <t>-72,86; 60,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,45; 40,86</t>
+          <t>-77,69; 37,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 21,22</t>
+          <t>-87,95; 32,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,88; 27,14</t>
+          <t>-53,0; 33,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 11,0</t>
+          <t>-62,16; 14,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,84; -37,57</t>
+          <t>-87,88; -37,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,48</t>
+          <t>-4,89; 2,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,04</t>
+          <t>-6,72; 0,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,93</t>
+          <t>-6,13; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 5,25</t>
+          <t>-3,1; 4,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -0,03</t>
+          <t>-6,64; -0,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -2,71</t>
+          <t>-8,0; -2,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,54</t>
+          <t>-2,6; 2,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -0,88</t>
+          <t>-5,35; -0,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -1,68</t>
+          <t>-6,07; -1,71</t>
         </is>
       </c>
     </row>
@@ -1215,27 +1215,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 97,51</t>
+          <t>-72,78; 93,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,07; 20,79</t>
+          <t>-89,06; 47,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,89; 42,16</t>
+          <t>-86,91; 25,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 185,26</t>
+          <t>-47,99; 150,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,12; 28,93</t>
+          <t>-91,91; 35,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,57; 70,5</t>
+          <t>-43,36; 78,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,85; -18,9</t>
+          <t>-82,92; -15,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,84; -38,33</t>
+          <t>-91,1; -40,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,08</t>
+          <t>-0,52; 5,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,15</t>
+          <t>-1,65; 3,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,23</t>
+          <t>-3,23; 0,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,93</t>
+          <t>-3,9; 3,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 0,03</t>
+          <t>-6,1; 0,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 0,45</t>
+          <t>-5,76; 0,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,14</t>
+          <t>-1,5; 3,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,78</t>
+          <t>-2,95; 0,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,18</t>
+          <t>-3,82; -0,18</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 666,74</t>
+          <t>-27,05; 801,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 445,25</t>
+          <t>-62,91; 367,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,18; 79,25</t>
+          <t>-57,7; 86,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,7; 16,94</t>
+          <t>-81,89; 17,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-84,12; 17,92</t>
+          <t>-84,08; 14,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 129,09</t>
+          <t>-35,11; 124,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 38,97</t>
+          <t>-67,69; 34,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,36; 1,07</t>
+          <t>-83,44; -1,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,96</t>
+          <t>-1,25; 1,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,88</t>
+          <t>-2,23; 0,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,88</t>
+          <t>-3,7; -1,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,54</t>
+          <t>-1,91; 1,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,14</t>
+          <t>-3,28; -0,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -1,33</t>
+          <t>-4,57; -1,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,27</t>
+          <t>-1,11; 1,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,24</t>
+          <t>-2,38; -0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,7</t>
+          <t>-3,7; -1,71</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 65,78</t>
+          <t>-28,2; 61,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 30,64</t>
+          <t>-49,63; 29,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,35; -29,27</t>
+          <t>-81,08; -35,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 42,21</t>
+          <t>-35,07; 40,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-61,94; -2,67</t>
+          <t>-60,88; -4,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,75; -36,7</t>
+          <t>-80,48; -38,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 35,77</t>
+          <t>-23,71; 35,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,87; -5,46</t>
+          <t>-49,0; -3,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,48; -46,52</t>
+          <t>-77,64; -46,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,19</t>
+          <t>-3,03; 3,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,5</t>
+          <t>-3,13; 3,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,57</t>
+          <t>-4,17; 1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,22</t>
+          <t>-2,6; 4,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 5,23</t>
+          <t>-2,86; 4,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 1,87</t>
+          <t>-4,56; 1,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,03</t>
+          <t>-2,11; 2,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,31</t>
+          <t>-1,94; 3,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,97</t>
+          <t>-3,44; 0,78</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,53; 320,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 253,53</t>
+          <t>-74,41; 269,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,67; 234,37</t>
+          <t>-89,1; 154,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 312,83</t>
+          <t>-60,73; 284,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,12; 318,92</t>
+          <t>-63,43; 241,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,93; 133,49</t>
+          <t>-83,5; 128,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 161,13</t>
+          <t>-52,09; 134,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,96; 163,29</t>
+          <t>-47,84; 149,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,16; 63,76</t>
+          <t>-75,17; 48,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 2,86</t>
+          <t>-4,68; 2,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,87</t>
+          <t>-4,73; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,98; -2,2</t>
+          <t>-7,87; -2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,5</t>
+          <t>-4,67; 1,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,81</t>
+          <t>-4,57; 0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 0,16</t>
+          <t>-5,61; -0,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,21</t>
+          <t>-3,35; 1,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,54</t>
+          <t>-3,84; 0,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; -1,62</t>
+          <t>-5,77; -1,66</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 71,88</t>
+          <t>-58,9; 70,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,39; 58,93</t>
+          <t>-63,04; 57,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,51</t>
+          <t>-99,73; -41,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,86; 60,73</t>
+          <t>-72,14; 45,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,69; 37,29</t>
+          <t>-75,16; 37,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,95; 32,97</t>
+          <t>-87,75; 23,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,0; 33,09</t>
+          <t>-51,6; 32,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 14,6</t>
+          <t>-59,86; 17,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,88; -37,66</t>
+          <t>-87,55; -35,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,43</t>
+          <t>-5,2; 2,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,35</t>
+          <t>-6,58; -0,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 0,44</t>
+          <t>-6,28; 0,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 4,87</t>
+          <t>-2,95; 4,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,64; -0,24</t>
+          <t>-6,56; 0,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -2,64</t>
+          <t>-8,44; -2,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,77</t>
+          <t>-3,14; 2,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -0,88</t>
+          <t>-5,76; -0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -1,71</t>
+          <t>-6,11; -1,69</t>
         </is>
       </c>
     </row>
@@ -1215,27 +1215,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-72,78; 93,7</t>
+          <t>-71,51; 101,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 47,36</t>
+          <t>-90,76; 13,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,91; 25,71</t>
+          <t>-86,48; 41,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 150,15</t>
+          <t>-46,62; 176,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,91; 35,33</t>
+          <t>-92,7; 33,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 78,83</t>
+          <t>-50,12; 73,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,92; -15,28</t>
+          <t>-85,85; -18,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-91,1; -40,17</t>
+          <t>-90,32; -38,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,09</t>
+          <t>-0,79; 5,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,02</t>
+          <t>-1,46; 3,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,17</t>
+          <t>-3,39; 0,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 3,17</t>
+          <t>-3,97; 3,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,13</t>
+          <t>-5,78; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 0,22</t>
+          <t>-5,77; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,18</t>
+          <t>-1,55; 3,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,78</t>
+          <t>-3,08; 0,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,18</t>
+          <t>-3,96; -0,35</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 801,43</t>
+          <t>-36,85; 645,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,91; 367,91</t>
+          <t>-60,35; 499,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 86,98</t>
+          <t>-56,84; 114,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,89; 17,93</t>
+          <t>-82,87; 31,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-84,08; 14,47</t>
+          <t>-81,99; 28,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 124,67</t>
+          <t>-35,08; 126,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 34,39</t>
+          <t>-68,12; 33,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,44; -1,37</t>
+          <t>-84,0; -8,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,83</t>
+          <t>-1,43; 1,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,84</t>
+          <t>-2,18; 0,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,07</t>
+          <t>-3,79; -1,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,52</t>
+          <t>-1,94; 1,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; -0,2</t>
+          <t>-3,37; -0,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -1,6</t>
+          <t>-4,47; -1,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,21</t>
+          <t>-1,22; 1,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,17</t>
+          <t>-2,34; -0,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,71</t>
+          <t>-3,71; -1,72</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 61,66</t>
+          <t>-30,8; 66,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 29,61</t>
+          <t>-49,13; 25,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,08; -35,09</t>
+          <t>-79,88; -31,95</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 40,78</t>
+          <t>-35,0; 45,41</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-60,88; -4,17</t>
+          <t>-61,92; -3,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,48; -38,28</t>
+          <t>-79,56; -32,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 35,79</t>
+          <t>-25,63; 35,94</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -3,91</t>
+          <t>-49,36; -4,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,64; -46,27</t>
+          <t>-76,34; -46,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,52</t>
+          <t>-3,01; 4,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,48</t>
+          <t>-2,84; 5,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,33</t>
+          <t>-4,89; 1,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,98</t>
+          <t>-3,02; 3,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,69</t>
+          <t>-3,1; 3,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,66</t>
+          <t>-4,24; 1,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,92</t>
+          <t>-1,99; 3,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,1</t>
+          <t>-1,79; 3,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,78</t>
+          <t>-3,69; 0,63</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30,08%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-38,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>6,23%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-38,94%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,39%</t>
+          <t>-43,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-36,55%</t>
+          <t>-40,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,53; 320,14</t>
+          <t>-61,25; 272,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 269,82</t>
+          <t>-60,02; 279,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,1; 154,07</t>
+          <t>-86,48; 124,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,73; 284,49</t>
+          <t>-73,98; 277,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 241,02</t>
+          <t>-76,53; 270,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,5; 128,05</t>
+          <t>-89,05; 160,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 134,25</t>
+          <t>-45,7; 156,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,84; 149,81</t>
+          <t>-41,56; 176,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 48,8</t>
+          <t>-78,97; 34,94</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,68</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,29</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-4,72</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-1,13</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>-1,62</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,72</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-3,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,84</t>
+          <t>-4,55; 1,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 2,06</t>
+          <t>-4,83; 0,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -2,0</t>
+          <t>-5,71; 0,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,19</t>
+          <t>-4,3; 2,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 0,85</t>
+          <t>-4,79; 1,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -0,07</t>
+          <t>-7,69; -2,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,05</t>
+          <t>-3,64; 1,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,64</t>
+          <t>-4,03; 0,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; -1,66</t>
+          <t>-5,86; -1,74</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-35,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-41,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-58,44%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-10,59%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-22,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-82,04%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-35,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-41,83%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-59,21%</t>
+          <t>-82,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-70,52%</t>
+          <t>-70,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,9; 70,89</t>
+          <t>-74,11; 41,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,04; 57,55</t>
+          <t>-77,45; 40,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-99,73; -41,98</t>
+          <t>-88,01; 30,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 45,72</t>
+          <t>-56,4; 64,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,16; 37,71</t>
+          <t>-61,4; 51,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 23,36</t>
+          <t>-95,25; -40,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,6; 32,75</t>
+          <t>-55,88; 27,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,86; 17,96</t>
+          <t>-62,3; 11,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-87,55; -35,58</t>
+          <t>-88,06; -35,23</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,93</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,93</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,47</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,93</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>-3,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,49</t>
+          <t>-3,28; 5,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; -0,06</t>
+          <t>-6,79; -0,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,83</t>
+          <t>-8,6; -2,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,85</t>
+          <t>-4,75; 2,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 0,2</t>
+          <t>-6,58; 0,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -2,62</t>
+          <t>-5,56; 1,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,55</t>
+          <t>-2,94; 2,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; -0,98</t>
+          <t>-5,44; -0,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -1,69</t>
+          <t>-5,96; -1,4</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-63,9%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-22,38%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-60,17%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-50,72%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20,23%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-63,9%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-41,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-75,27%</t>
+          <t>-72,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,51; 101,94</t>
+          <t>-48,46; 185,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,76; 13,92</t>
+          <t>-92,12; 28,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 41,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 176,58</t>
+          <t>-70,32; 97,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,7; 33,67</t>
+          <t>-90,07; 20,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,81; 69,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,12; 73,47</t>
+          <t>-48,57; 70,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,85; -18,94</t>
+          <t>-84,85; -18,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,32; -38,71</t>
+          <t>-89,21; -29,33</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,76</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,75</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,71</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,76</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,67</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>-2,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,16</t>
+          <t>-4,28; 2,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,25</t>
+          <t>-6,13; 0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,16</t>
+          <t>-6,01; 0,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,6</t>
+          <t>-0,62; 5,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,61</t>
+          <t>-1,55; 3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 0,45</t>
+          <t>-3,54; 0,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,19</t>
+          <t>-1,17; 3,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,71</t>
+          <t>-3,16; 0,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -0,35</t>
+          <t>-3,86; -0,39</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-7,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-53,21%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-53,13%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>118,88%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>39,89%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-75,36%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-7,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-53,21%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-51,43%</t>
+          <t>-76,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-56,35%</t>
+          <t>-58,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 645,74</t>
+          <t>-62,18; 79,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 499,99</t>
+          <t>-82,7; 16,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>-85,18; 14,93</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-34,21; 666,74</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-63,17; 445,25</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-56,84; 114,95</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-82,87; 31,2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-81,99; 28,06</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 126,51</t>
+          <t>-27,98; 129,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 33,06</t>
+          <t>-66,82; 38,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,0; -8,0</t>
+          <t>-82,17; -5,15</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,97</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-2,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-2,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,95</t>
+          <t>-1,92; 1,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,8</t>
+          <t>-3,52; -0,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -1,04</t>
+          <t>-4,53; -1,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,64</t>
+          <t>-1,41; 1,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,13</t>
+          <t>-2,23; 0,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; -1,39</t>
+          <t>-3,69; -0,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,28</t>
+          <t>-1,34; 1,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,14</t>
+          <t>-2,42; -0,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; -1,72</t>
+          <t>-3,7; -1,69</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-3,43%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-39,43%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-64,78%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>8,14%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-19,09%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-62,86%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-3,43%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-39,43%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-64,35%</t>
+          <t>-62,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-63,59%</t>
+          <t>-63,65%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 66,89</t>
+          <t>-34,68; 42,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 25,8</t>
+          <t>-61,94; -2,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-79,88; -31,95</t>
+          <t>-80,71; -36,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 45,41</t>
+          <t>-31,31; 65,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -3,66</t>
+          <t>-48,44; 30,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,56; -32,97</t>
+          <t>-80,36; -29,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 35,94</t>
+          <t>-28,09; 35,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,36; -4,05</t>
+          <t>-49,87; -5,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,34; -46,09</t>
+          <t>-76,49; -46,32</t>
         </is>
       </c>
     </row>
